--- a/Clase/RUC_Clase.xlsx
+++ b/Clase/RUC_Clase.xlsx
@@ -680,13 +680,13 @@
         <v>2.354096686279302</v>
       </c>
       <c r="C2" s="2">
-        <v>109.9152459301427</v>
+        <v>109.5894924334297</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>2.587511162157234</v>
+        <v>2.579842609885675</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -813,7 +813,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="2">
-        <v>3.277078953177017</v>
+        <v>3.277078953177016</v>
       </c>
       <c r="C10" s="2">
         <v>109.5935146729494</v>
@@ -822,7 +822,7 @@
         <v>6</v>
       </c>
       <c r="E10" s="2">
-        <v>3.59146600339419</v>
+        <v>3.591466003394191</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -1071,7 +1071,7 @@
         <v>2.050236585551548</v>
       </c>
       <c r="C25" s="2">
-        <v>106.520426094603</v>
+        <v>106.5204260946029</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>6</v>
@@ -1377,13 +1377,13 @@
         <v>2.000273347521607</v>
       </c>
       <c r="C43" s="2">
-        <v>111.0353345676262</v>
+        <v>111.0353345676261</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E43" s="2">
-        <v>2.221010203687672</v>
+        <v>2.221010203687671</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -1408,10 +1408,10 @@
         <v>49</v>
       </c>
       <c r="B45" s="2">
-        <v>0.5973104237677945</v>
+        <v>0.5973104237677944</v>
       </c>
       <c r="C45" s="2">
-        <v>115.1438838516155</v>
+        <v>115.1438838516156</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>6</v>
@@ -1972,13 +1972,13 @@
         <v>12.20496104551848</v>
       </c>
       <c r="C78" s="2">
-        <v>116.2767296048998</v>
+        <v>116.2767296048999</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E78" s="2">
-        <v>14.19152955328088</v>
+        <v>14.19152955328089</v>
       </c>
     </row>
     <row r="79" spans="1:5">
